--- a/scripts/test-data/test-data-003-mockpass-import-demo.xlsx
+++ b/scripts/test-data/test-data-003-mockpass-import-demo.xlsx
@@ -460,12 +460,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.996339" customWidth="1" style="4" min="1" max="1"/>
     <col width="14.282054" customWidth="1" style="4" min="2" max="2"/>
-    <col width="15.282054" customWidth="1" style="4" min="3" max="3"/>
+    <col width="42" customWidth="1" style="4" min="3" max="3"/>
     <col width="28.139196" customWidth="1" style="4" min="4" max="4"/>
     <col width="11.424911" customWidth="1" style="5" min="5" max="5"/>
     <col width="15.282054" customWidth="1" style="4" min="6" max="6"/>
@@ -494,70 +494,75 @@
       </c>
       <c r="C1" s="6" t="inlineStr">
         <is>
+          <t>MockPassPersonId</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
           <t>IdentityNumber</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>FullName</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>DateOfBirth</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>NationalityCode</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>CitizenshipStatusCode</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>StudentNumber</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>AcademicYear</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>LevelCode</t>
         </is>
       </c>
-      <c r="K1" s="6" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>ClassCode</t>
         </is>
       </c>
-      <c r="L1" s="7" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>StartDate</t>
         </is>
       </c>
-      <c r="M1" s="6" t="inlineStr">
+      <c r="N1" s="6" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="N1" s="6" t="inlineStr">
+      <c r="O1" s="6" t="inlineStr">
         <is>
           <t>Mobile</t>
         </is>
       </c>
-      <c r="O1" s="6" t="inlineStr">
+      <c r="P1" s="6" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="P1" s="6" t="inlineStr">
+      <c r="Q1" s="6" t="inlineStr">
         <is>
           <t>TemplateRow</t>
         </is>
@@ -570,61 +575,66 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
+          <t>ea431f89-97db-5420-ad13-17a6dfe09743</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
           <t>S7000061Q</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO003 Daphne Lee NUS</t>
         </is>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="F2" s="5" t="n">
         <v>38500</v>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>NUS-2026-061</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>POST_SEC</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="L2" s="4" t="inlineStr">
         <is>
           <t>NUS-S4-13</t>
         </is>
       </c>
-      <c r="L2" s="5" t="n">
+      <c r="M2" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="N2" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo003.daphne.lee.nus.061@student.example.test</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>+6591000061</t>
         </is>
       </c>
-      <c r="O2" s="4" t="inlineStr">
+      <c r="P2" s="4" t="inlineStr">
         <is>
           <t>61 Education Avenue, Singapore 100061</t>
         </is>
@@ -637,61 +647,66 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
+          <t>c15ea717-478f-54fb-923f-48b3e778b32a</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
           <t>S7000062R</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO003 Elias Goh NTU</t>
         </is>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="F3" s="5" t="n">
         <v>39339</v>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>NTU-2026-062</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>POST_SEC</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>NTU-S3-13</t>
         </is>
       </c>
-      <c r="L3" s="5" t="n">
+      <c r="M3" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo003.elias.goh.ntu.062@student.example.test</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>+6591000062</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>62 Education Avenue, Singapore 100062</t>
         </is>
@@ -704,61 +719,66 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
+          <t>5bc4d535-da31-54de-9c06-cc1d686ccbec</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
           <t>S7000063T</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO003 Farah Rahman SMU</t>
         </is>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="F4" s="5" t="n">
         <v>37287</v>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>SMU-2026-063</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>POST_SEC</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>SMU-P6-13</t>
         </is>
       </c>
-      <c r="L4" s="5" t="n">
+      <c r="M4" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo003.farah.rahman.smu.063@student.example.test</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>+6591000063</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>63 Education Avenue, Singapore 100063</t>
         </is>
@@ -771,61 +791,66 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
+          <t>f5db42b4-05d3-568b-833e-2fc6ffa04ea1</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
           <t>S7000064U</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO003 Gideon Koh SUTD</t>
         </is>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="F5" s="5" t="n">
         <v>40152</v>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>SUTD-2026-064</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>POST_SEC</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>SUTD-S2-13</t>
         </is>
       </c>
-      <c r="L5" s="5" t="n">
+      <c r="M5" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo003.gideon.koh.sutd.064@student.example.test</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>+6591000064</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>64 Education Avenue, Singapore 100064</t>
         </is>
@@ -838,61 +863,66 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
+          <t>7809497a-eb1d-5efd-b98a-b9c1d2a47122</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
           <t>S7000065V</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO003 Hazel Ng SIT</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="F6" s="5" t="n">
         <v>37094</v>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>SIT-2026-065</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>BACHELOR</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>SIT-UG-13</t>
         </is>
       </c>
-      <c r="L6" s="5" t="n">
+      <c r="M6" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo003.hazel.ng.sit.065@student.example.test</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>+6591000065</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>65 Education Avenue, Singapore 100065</t>
         </is>
@@ -905,61 +935,66 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
+          <t>ca7110b4-ff7b-5d94-ac2f-ff865e40d140</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
           <t>S7000066W</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO003 Isaac Chua NUS</t>
         </is>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="F7" s="5" t="n">
         <v>35506</v>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>NUS-2026-066</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>MASTER</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>NUS-PG-14</t>
         </is>
       </c>
-      <c r="L7" s="5" t="n">
+      <c r="M7" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo003.isaac.chua.nus.066@student.example.test</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="O7" s="4" t="inlineStr">
         <is>
           <t>+6591000066</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="P7" s="4" t="inlineStr">
         <is>
           <t>66 Education Avenue, Singapore 100066</t>
         </is>
@@ -972,61 +1007,66 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
+          <t>415b6944-0339-5585-ab46-eb2b64bc3050</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
           <t>S7000067X</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO003 Jia Min Seah NTU</t>
         </is>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="F8" s="5" t="n">
         <v>39730</v>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>NTU-2026-067</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>PHD</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>NTU-DR-14</t>
         </is>
       </c>
-      <c r="L8" s="5" t="n">
+      <c r="M8" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo003.jia.min.seah.ntu.067@student.example.test</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>+6591000067</t>
         </is>
       </c>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="P8" s="4" t="inlineStr">
         <is>
           <t>67 Education Avenue, Singapore 100067</t>
         </is>
@@ -1039,61 +1079,66 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
+          <t>4085e345-66b7-5110-92f6-542d900a1e3f</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
           <t>S7000068Y</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO003 Keira Low SMU</t>
         </is>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="F9" s="5" t="n">
         <v>37729</v>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>SMU-2026-068</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>BACHELOR</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>SMU-UG-14</t>
         </is>
       </c>
-      <c r="L9" s="5" t="n">
+      <c r="M9" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo003.keira.low.smu.068@student.example.test</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="O9" s="4" t="inlineStr">
         <is>
           <t>+6591000068</t>
         </is>
       </c>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="P9" s="4" t="inlineStr">
         <is>
           <t>68 Education Avenue, Singapore 100068</t>
         </is>
@@ -1106,61 +1151,66 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
+          <t>8423c59a-acf9-57d6-9a4e-9ebaca86bf68</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
           <t>S7000069Z</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO003 Leon Ho SUTD</t>
         </is>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="F10" s="5" t="n">
         <v>36336</v>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>SUTD-2026-069</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>MASTER</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>SUTD-PG-14</t>
         </is>
       </c>
-      <c r="L10" s="5" t="n">
+      <c r="M10" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="N10" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo003.leon.ho.sutd.069@student.example.test</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>+6591000069</t>
         </is>
       </c>
-      <c r="O10" s="4" t="inlineStr">
+      <c r="P10" s="4" t="inlineStr">
         <is>
           <t>69 Education Avenue, Singapore 100069</t>
         </is>
@@ -1173,61 +1223,66 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
+          <t>4a212557-93a5-5d64-8fa6-54e6035ce422</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
           <t>S7000070A</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO003 Mira Das SIT</t>
         </is>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="F11" s="5" t="n">
         <v>34676</v>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>SIT-2026-070</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>PHD</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>SIT-DR-14</t>
         </is>
       </c>
-      <c r="L11" s="5" t="n">
+      <c r="M11" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="N11" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo003.mira.das.sit.070@student.example.test</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="O11" s="4" t="inlineStr">
         <is>
           <t>+6591000070</t>
         </is>
       </c>
-      <c r="O11" s="4" t="inlineStr">
+      <c r="P11" s="4" t="inlineStr">
         <is>
           <t>70 Education Avenue, Singapore 100070</t>
         </is>
@@ -1240,61 +1295,66 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
+          <t>ef0e51ee-82fb-5377-aa4d-bc1f0445fd84</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
           <t>S7000071B</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO003 Nolan Teo NUS</t>
         </is>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="F12" s="5" t="n">
         <v>38797</v>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>NUS-2026-071</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>POST_SEC</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>NUS-S4-15</t>
         </is>
       </c>
-      <c r="L12" s="5" t="n">
+      <c r="M12" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="N12" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo003.nolan.teo.nus.071@student.example.test</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>+6591000071</t>
         </is>
       </c>
-      <c r="O12" s="4" t="inlineStr">
+      <c r="P12" s="4" t="inlineStr">
         <is>
           <t>71 Education Avenue, Singapore 100071</t>
         </is>
@@ -1307,61 +1367,66 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
+          <t>ecc8156e-eefb-5d9b-86e3-4d032805d275</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
           <t>S7000072C</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO003 Olivia Chan NTU</t>
         </is>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="F13" s="5" t="n">
         <v>40309</v>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>NTU-2026-072</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>POST_SEC</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>NTU-S3-15</t>
         </is>
       </c>
-      <c r="L13" s="5" t="n">
+      <c r="M13" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="N13" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo003.olivia.chan.ntu.072@student.example.test</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="O13" s="4" t="inlineStr">
         <is>
           <t>+6591000072</t>
         </is>
       </c>
-      <c r="O13" s="4" t="inlineStr">
+      <c r="P13" s="4" t="inlineStr">
         <is>
           <t>72 Education Avenue, Singapore 100072</t>
         </is>
@@ -1374,61 +1439,66 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
+          <t>aab755a8-b08e-5ee6-a94a-1abf79dae620</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
           <t>S7000073D</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO003 Pranav Menon SMU</t>
         </is>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="F14" s="5" t="n">
         <v>36799</v>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>SMU-2026-073</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>POST_SEC</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>SMU-P6-15</t>
         </is>
       </c>
-      <c r="L14" s="5" t="n">
+      <c r="M14" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="N14" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo003.pranav.menon.smu.073@student.example.test</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>+6591000073</t>
         </is>
       </c>
-      <c r="O14" s="4" t="inlineStr">
+      <c r="P14" s="4" t="inlineStr">
         <is>
           <t>73 Education Avenue, Singapore 100073</t>
         </is>
@@ -1441,61 +1511,66 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
+          <t>4ff67eeb-c9e3-579b-922d-a9c80659cc3a</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
           <t>S7000074E</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO003 Renee Yap SUTD</t>
         </is>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="F15" s="5" t="n">
         <v>35080</v>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>SUTD-2026-074</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>POST_SEC</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>SUTD-S2-15</t>
         </is>
       </c>
-      <c r="L15" s="5" t="n">
+      <c r="M15" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="N15" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo003.renee.yap.sutd.074@student.example.test</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="O15" s="4" t="inlineStr">
         <is>
           <t>+6591000074</t>
         </is>
       </c>
-      <c r="O15" s="4" t="inlineStr">
+      <c r="P15" s="4" t="inlineStr">
         <is>
           <t>74 Education Avenue, Singapore 100074</t>
         </is>
@@ -1508,61 +1583,66 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
+          <t>05279da0-e919-5739-9cbf-e5ff367bf92f</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
           <t>S7000075F</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO003 Samuel Tay SIT</t>
         </is>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="F16" s="5" t="n">
         <v>38175</v>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>SIT-2026-075</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>BACHELOR</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>SIT-UG-15</t>
         </is>
       </c>
-      <c r="L16" s="5" t="n">
+      <c r="M16" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="N16" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo003.samuel.tay.sit.075@student.example.test</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>+6591000075</t>
         </is>
       </c>
-      <c r="O16" s="4" t="inlineStr">
+      <c r="P16" s="4" t="inlineStr">
         <is>
           <t>75 Education Avenue, Singapore 100075</t>
         </is>
@@ -1575,61 +1655,66 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
+          <t>c7011a1e-2089-5ba4-8c9a-d87db4d74311</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
           <t>S7000076G</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO003 Tara Nair NUS</t>
         </is>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="F17" s="5" t="n">
         <v>39775</v>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>NUS-2026-076</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>MASTER</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="L17" s="4" t="inlineStr">
         <is>
           <t>NUS-PG-16</t>
         </is>
       </c>
-      <c r="L17" s="5" t="n">
+      <c r="M17" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo003.tara.nair.nus.076@student.example.test</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="O17" s="4" t="inlineStr">
         <is>
           <t>+6591000076</t>
         </is>
       </c>
-      <c r="O17" s="4" t="inlineStr">
+      <c r="P17" s="4" t="inlineStr">
         <is>
           <t>76 Education Avenue, Singapore 100076</t>
         </is>
@@ -1642,61 +1727,66 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
+          <t>146cbf24-cf60-5bc0-a15b-c9000b6dbbcc</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
           <t>S7000077H</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO003 Vikram Singh NTU</t>
         </is>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="F18" s="5" t="n">
         <v>37531</v>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>NTU-2026-077</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>PHD</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>NTU-DR-16</t>
         </is>
       </c>
-      <c r="L18" s="5" t="n">
+      <c r="M18" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="N18" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo003.vikram.singh.ntu.077@student.example.test</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>+6591000077</t>
         </is>
       </c>
-      <c r="O18" s="4" t="inlineStr">
+      <c r="P18" s="4" t="inlineStr">
         <is>
           <t>77 Education Avenue, Singapore 100077</t>
         </is>
@@ -1707,63 +1797,64 @@
       <c r="B19" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>A7000078J</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO003 Avery Tan SMU</t>
         </is>
       </c>
-      <c r="E19" s="5" t="n">
+      <c r="F19" s="5" t="n">
         <v>38029</v>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>SMU-2026-078</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>BACHELOR</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>SMU-UG-16</t>
         </is>
       </c>
-      <c r="L19" s="5" t="n">
+      <c r="M19" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="N19" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo003.avery.tan.smu.078@student.example.test</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="O19" s="4" t="inlineStr">
         <is>
           <t>+6591000078</t>
         </is>
       </c>
-      <c r="O19" s="4" t="inlineStr">
+      <c r="P19" s="4" t="inlineStr">
         <is>
           <t>78 Education Avenue, Singapore 100078</t>
         </is>
@@ -1776,57 +1867,62 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
+          <t>a47c1e33-7c56-57ab-9925-950603fae26a</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
           <t>S7000079K</t>
         </is>
       </c>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="5" t="n">
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="5" t="n">
         <v>36010</v>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>SUTD-2026-079</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>MASTER</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>SUTD-PG-16</t>
         </is>
       </c>
-      <c r="L20" s="5" t="n">
+      <c r="M20" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="N20" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo003.bianca.lim.sutd.079@student.example.test</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>+6591000079</t>
         </is>
       </c>
-      <c r="O20" s="4" t="inlineStr">
+      <c r="P20" s="4" t="inlineStr">
         <is>
           <t>79 Education Avenue, Singapore 100079</t>
         </is>
@@ -1839,61 +1935,66 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
+          <t>c21c0684-730c-5d13-9665-76f638bc8051</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
           <t>S7000080L</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO003 Caleb Wong SIT</t>
         </is>
       </c>
-      <c r="E21" s="5" t="n">
+      <c r="F21" s="5" t="n">
         <v>34292</v>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>SIT-2026-080</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>PHD</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>SIT-DR-16</t>
         </is>
       </c>
-      <c r="L21" s="5" t="n">
+      <c r="M21" s="5" t="n">
         <v>33927</v>
       </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="N21" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo003.caleb.wong.sit.080@student.example.test</t>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr">
+      <c r="O21" s="4" t="inlineStr">
         <is>
           <t>+6591000080</t>
         </is>
       </c>
-      <c r="O21" s="4" t="inlineStr">
+      <c r="P21" s="4" t="inlineStr">
         <is>
           <t>80 Education Avenue, Singapore 100080</t>
         </is>
